--- a/nr-rm-adeli/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/nr-rm-adeli/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:53:29+00:00</t>
+    <t>2024-10-29T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -8405,7 +8405,7 @@
         <v>273</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>275</v>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>81</v>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>81</v>
